--- a/www/download/IND.labour_force_value.s.mv.rpO2.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>128728.959</t>
+          <t>128728959487.377</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>134212.763</t>
+          <t>134212763186.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>111334.831</t>
+          <t>111334831392.766</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>116721.962</t>
+          <t>116721962363.121</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>195438.848</t>
+          <t>195438848367.3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>245388.881</t>
+          <t>245388881404.374</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>251824.732</t>
+          <t>251824732451.575</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>269489.782</t>
+          <t>269489781627.388</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>309259.456</t>
+          <t>309259455569.857</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>365740.97</t>
+          <t>365740970171.243</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>424482.81</t>
+          <t>424482809605.092</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>436761.448</t>
+          <t>436761447563.401</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>409691.186</t>
+          <t>409691185975.149</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>393918.751</t>
+          <t>393918751393.925</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>302786.126</t>
+          <t>302786126144.242</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>71058.665</t>
+          <t>71058665003.9139</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>74802.948</t>
+          <t>74802947813.3526</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>49389.455</t>
+          <t>49389455253.1492</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>55627.044</t>
+          <t>55627044274.873</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>78000.887</t>
+          <t>78000887274.5964</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>108845.082</t>
+          <t>108845082110.655</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>121546.901</t>
+          <t>121546901181.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>125243.479</t>
+          <t>125243478836.554</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>130730.395</t>
+          <t>130730394798.389</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>133691.349</t>
+          <t>133691349410.322</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>149484.37</t>
+          <t>149484369934.041</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>163181.843</t>
+          <t>163181843419.012</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>133097.372</t>
+          <t>133097371923.262</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>123250.021</t>
+          <t>123250020895.207</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>84077.175</t>
+          <t>84077175470.3973</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>106022.267</t>
+          <t>106022267358.486</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>93279.952</t>
+          <t>93279951884.4703</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>74742.936</t>
+          <t>74742936000.0389</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>79012.475</t>
+          <t>79012474823.7041</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>102863.902</t>
+          <t>102863901750.89</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>149843.326</t>
+          <t>149843325530.296</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>157777.498</t>
+          <t>157777497852.002</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>174773.04</t>
+          <t>174773039686.628</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>198059.038</t>
+          <t>198059037885.596</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>198023.051</t>
+          <t>198023051002.279</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>244024.099</t>
+          <t>244024098852.708</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>234852.625</t>
+          <t>234852624604.991</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>196012.378</t>
+          <t>196012377786.7</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>200553.711</t>
+          <t>200553711489.969</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>149712.732</t>
+          <t>149712731666.511</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7244.587</t>
+          <t>7244587132.91932</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6406.687</t>
+          <t>6406687210.59621</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4327.614</t>
+          <t>4327613586.92999</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5212.709</t>
+          <t>5212709455.84297</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5933.319</t>
+          <t>5933318720.33884</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6799.335</t>
+          <t>6799335398.44506</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9011.457</t>
+          <t>9011457252.64496</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10328.873</t>
+          <t>10328873176.8992</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>12121.562</t>
+          <t>12121561860.7329</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13536.979</t>
+          <t>13536978627.0777</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>14194.325</t>
+          <t>14194324684.7391</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>15770.307</t>
+          <t>15770307074.0244</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>15470.861</t>
+          <t>15470861316.4409</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>16882.437</t>
+          <t>16882437277.8031</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>13909.888</t>
+          <t>13909888089.889</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>308461.142</t>
+          <t>308461142342.603</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>300186.997</t>
+          <t>300186997276.44</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>278415.09</t>
+          <t>278415090483.5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>286836.887</t>
+          <t>286836887303.641</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>288186.413</t>
+          <t>288186413409.181</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>385011.415</t>
+          <t>385011414678.925</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>396183.099</t>
+          <t>396183098522.417</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>354516.368</t>
+          <t>354516367889.615</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>342588.643</t>
+          <t>342588642520.079</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>394906.182</t>
+          <t>394906181891.423</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>434084.809</t>
+          <t>434084808817.286</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>483209.321</t>
+          <t>483209321447.791</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>505255.298</t>
+          <t>505255297906.99</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>559374.35</t>
+          <t>559374349690.16</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>434458.925</t>
+          <t>434458925428.849</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>179632.328</t>
+          <t>179632328474.476</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>178099.743</t>
+          <t>178099742789.913</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>148814.657</t>
+          <t>148814656769.713</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>167242.102</t>
+          <t>167242102044.323</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>226343.285</t>
+          <t>226343284673.337</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>348730.203</t>
+          <t>348730203472.606</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>404997.799</t>
+          <t>404997799265.789</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>357296.836</t>
+          <t>357296836484.999</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>386282.47</t>
+          <t>386282469840.884</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>397795.039</t>
+          <t>397795038845.081</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>486347.328</t>
+          <t>486347328079.469</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>495718.402</t>
+          <t>495718402195.013</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>425532.084</t>
+          <t>425532084076.548</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>404191.295</t>
+          <t>404191295032.342</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>291233.582</t>
+          <t>291233582416.568</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3765340.808</t>
+          <t>3765340807966.9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3764832.629</t>
+          <t>3764832628572.32</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3319883.871</t>
+          <t>3319883871055.19</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3028471.225</t>
+          <t>3028471224834.52</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2672580.777</t>
+          <t>2672580777190.66</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2847361.191</t>
+          <t>2847361190941.44</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3139986.535</t>
+          <t>3139986534854.72</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3273408.573</t>
+          <t>3273408573259.27</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3551766.363</t>
+          <t>3551766363373.7</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4038669.68</t>
+          <t>4038669679936.88</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4269741.358</t>
+          <t>4269741358435.59</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4149834.547</t>
+          <t>4149834547028.48</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4026841.188</t>
+          <t>4026841188123.32</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>4219911.185</t>
+          <t>4219911184886.92</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>4008648.704</t>
+          <t>4008648703682.05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3679.56</t>
+          <t>3679560174.57045</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4215.669</t>
+          <t>4215669352.83295</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2582.399</t>
+          <t>2582399419.52717</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3062.095</t>
+          <t>3062094919.98349</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4760.629</t>
+          <t>4760628584.19621</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6120.361</t>
+          <t>6120361259.43864</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7404.221</t>
+          <t>7404221082.68731</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8316.249</t>
+          <t>8316248586.5759</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>9925.407</t>
+          <t>9925406583.77338</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>9630.973</t>
+          <t>9630972627.13445</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>8023.258</t>
+          <t>8023257731.76363</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>7524.744</t>
+          <t>7524743525.83099</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>6745.957</t>
+          <t>6745957398.94311</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>6959.194</t>
+          <t>6959194174.35121</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>4808.167</t>
+          <t>4808166956.83725</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13628.448</t>
+          <t>13628447695.9014</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>23973.285</t>
+          <t>23973285307.9327</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16058.89</t>
+          <t>16058890379.7923</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19709.617</t>
+          <t>19709617351.4942</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25270.261</t>
+          <t>25270261372.3834</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>34198.19</t>
+          <t>34198190008.6647</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>43655.959</t>
+          <t>43655959250.9483</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>46026.499</t>
+          <t>46026499429.9474</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>53499.587</t>
+          <t>53499587142.9432</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>53038.621</t>
+          <t>53038621137.1042</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>65067.16</t>
+          <t>65067160304.7743</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>67765.383</t>
+          <t>67765383492.6031</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>56917.349</t>
+          <t>56917349416.0793</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>54507.301</t>
+          <t>54507301145.856</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>33290.934</t>
+          <t>33290933561.3381</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>823774.792</t>
+          <t>823774792455.282</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>734202.633</t>
+          <t>734202633283.81</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>608610.464</t>
+          <t>608610464431.683</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>680307.348</t>
+          <t>680307347520.619</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>883912.62</t>
+          <t>883912620160.659</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1247437.987</t>
+          <t>1247437986825.84</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1412061.321</t>
+          <t>1412061321476.26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1424199.361</t>
+          <t>1424199361072.08</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1495787.271</t>
+          <t>1495787270775.5</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1463511.055</t>
+          <t>1463511054984.46</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1545875.632</t>
+          <t>1545875632204.38</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>1655461.161</t>
+          <t>1655461160948.31</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1335795.542</t>
+          <t>1335795542350.91</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1294205.234</t>
+          <t>1294205233529.67</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>874409.266</t>
+          <t>874409265602.163</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>77132.639</t>
+          <t>77132639386.6304</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>75661.173</t>
+          <t>75661173253.8462</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>56192.066</t>
+          <t>56192065723.0916</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69843.569</t>
+          <t>69843568644.4059</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>83680.478</t>
+          <t>83680477882.0832</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>100520.975</t>
+          <t>100520975444.427</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>116478.484</t>
+          <t>116478484429.514</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>126990.22</t>
+          <t>126990219698.842</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>139933.004</t>
+          <t>139933004330.535</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>143513.66</t>
+          <t>143513659674.447</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>165872.064</t>
+          <t>165872063774.44</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>175790.18</t>
+          <t>175790180398.219</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>156754.831</t>
+          <t>156754830711.284</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>165767.223</t>
+          <t>165767222520.149</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>100690.356</t>
+          <t>100690356440.818</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>173473.606</t>
+          <t>173473606208.25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>174704.835</t>
+          <t>174704834875.22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>147271.81</t>
+          <t>147271810246.183</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>166520.536</t>
+          <t>166520535837.811</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>239831.9</t>
+          <t>239831899945.273</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>377842.287</t>
+          <t>377842286786.557</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>410120.024</t>
+          <t>410120024136.305</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>422602.653</t>
+          <t>422602652906.075</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>496950.483</t>
+          <t>496950482960.869</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>538296.221</t>
+          <t>538296221246.154</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>652033.796</t>
+          <t>652033795675.977</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>709369.792</t>
+          <t>709369791512.432</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>598493.91</t>
+          <t>598493909588.095</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>583967.88</t>
+          <t>583967880446.463</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>384449.627</t>
+          <t>384449627398.353</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3000.038</t>
+          <t>3000038107.18879</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3191.716</t>
+          <t>3191716225.04676</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3704.233</t>
+          <t>3704232875.29347</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4189.415</t>
+          <t>4189415327.61305</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2926.565</t>
+          <t>2926564636.23698</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8274.873</t>
+          <t>8274872663.89002</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13136.955</t>
+          <t>13136954690.2516</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11702.997</t>
+          <t>11702997139.3529</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>17171.46</t>
+          <t>17171460486.8661</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>12593.237</t>
+          <t>12593236728.7767</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10641.426</t>
+          <t>10641426361.0254</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>11532.173</t>
+          <t>11532173123.2544</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>13493.222</t>
+          <t>13493222003.8163</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>14588.933</t>
+          <t>14588932862.5181</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>8199.963</t>
+          <t>8199962899.39296</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>33488.481</t>
+          <t>33488481216.8285</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>34349.424</t>
+          <t>34349423889.9494</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>25116.302</t>
+          <t>25116302199.4243</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>29027.275</t>
+          <t>29027274566.1836</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>39544.916</t>
+          <t>39544915558.7742</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>47890.294</t>
+          <t>47890294126.587</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>55046.296</t>
+          <t>55046296362.5931</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>54657.297</t>
+          <t>54657297023.8824</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>67878.045</t>
+          <t>67878044960.2631</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>70951.844</t>
+          <t>70951844305.6079</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>77105.408</t>
+          <t>77105407846.6982</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>81218.692</t>
+          <t>81218692113.5921</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>68059.949</t>
+          <t>68059949448.5837</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>69798.852</t>
+          <t>69798852344.191</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>44703.794</t>
+          <t>44703794026.0536</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>495445.055</t>
+          <t>495445054872.8</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>463904.205</t>
+          <t>463904205327.532</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>379146.357</t>
+          <t>379146356790.576</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>428170.773</t>
+          <t>428170773062.117</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>601817.831</t>
+          <t>601817830705.459</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>844095.773</t>
+          <t>844095773065.141</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>900124.305</t>
+          <t>900124305256.691</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>927713.995</t>
+          <t>927713994831.829</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1045988.391</t>
+          <t>1045988390517.1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1087103.947</t>
+          <t>1087103946872.14</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1318373.68</t>
+          <t>1318373680425.65</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1336201.98</t>
+          <t>1336201979961.41</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1094588.276</t>
+          <t>1094588275688.68</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1071922.302</t>
+          <t>1071922302430.46</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>719867.838</t>
+          <t>719867837998.603</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>456147.466</t>
+          <t>456147465534.979</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>469686.858</t>
+          <t>469686857664.729</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>393849.391</t>
+          <t>393849390626.931</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>441161.209</t>
+          <t>441161209344.824</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>577930.272</t>
+          <t>577930272251.349</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>773708.904</t>
+          <t>773708904161.48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>847126.671</t>
+          <t>847126671003.136</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>877298.984</t>
+          <t>877298983720.582</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>972114.035</t>
+          <t>972114034840.153</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1053356.927</t>
+          <t>1053356927288.2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1246165.544</t>
+          <t>1246165543727.1</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1292037.67</t>
+          <t>1292037670190.38</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1123261.874</t>
+          <t>1123261873663.56</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>949489.222</t>
+          <t>949489222478.132</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>640794.14</t>
+          <t>640794139931.932</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>21714.362</t>
+          <t>21714361704.6126</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>23676.179</t>
+          <t>23676179384.161</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20064.38</t>
+          <t>20064380246.8133</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23178.235</t>
+          <t>23178234624.929</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>31041.184</t>
+          <t>31041184391.9394</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>53620.802</t>
+          <t>53620801737.1614</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>55288.836</t>
+          <t>55288836301.9557</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>60141.02</t>
+          <t>60141020370.3839</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>71005.342</t>
+          <t>71005342279.4953</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>75300.721</t>
+          <t>75300720689.0827</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>86221.488</t>
+          <t>86221487792.5292</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>118908.547</t>
+          <t>118908547366.182</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>100042.547</t>
+          <t>100042546515.007</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>110219.014</t>
+          <t>110219013586.523</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>82146.973</t>
+          <t>82146973162.7534</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20177.357</t>
+          <t>20177357268.3909</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17554.754</t>
+          <t>17554753578.3049</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15065.751</t>
+          <t>15065750741.507</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>20290.276</t>
+          <t>20290275947.819</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>26219.505</t>
+          <t>26219504679.4773</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>32331.205</t>
+          <t>32331204515.9424</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>38877.945</t>
+          <t>38877945185.4356</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>46017.459</t>
+          <t>46017458782.7337</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>53286.424</t>
+          <t>53286423598.8577</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>54171.401</t>
+          <t>54171401189.1096</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>56660.08</t>
+          <t>56660080023.5539</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>57315.666</t>
+          <t>57315665540.0065</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>55201.404</t>
+          <t>55201403883.1375</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>44252.878</t>
+          <t>44252878227.0984</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>25603.474</t>
+          <t>25603473529.9511</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>135348.974</t>
+          <t>135348973961.797</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>149300.946</t>
+          <t>149300945726.814</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>135727.156</t>
+          <t>135727156113.986</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>117891.597</t>
+          <t>117891597331.04</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>131790.454</t>
+          <t>131790453718.927</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>156588.384</t>
+          <t>156588384015.885</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>152953.219</t>
+          <t>152953219209.052</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>178622.139</t>
+          <t>178622138863.51</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>193135.87</t>
+          <t>193135870115.5</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>213974.079</t>
+          <t>213974079009.1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>219606.627</t>
+          <t>219606627379.451</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>223864.358</t>
+          <t>223864358246.161</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>212907.84</t>
+          <t>212907839697.493</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>214931.681</t>
+          <t>214931681438.448</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>165287.352</t>
+          <t>165287352396.749</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>934730.36</t>
+          <t>934730360093.258</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>781553.765</t>
+          <t>781553764908.421</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>763424.643</t>
+          <t>763424642770.148</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>663358.051</t>
+          <t>663358051255.426</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>683227.866</t>
+          <t>683227866429.509</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>935540.658</t>
+          <t>935540658107.165</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1119474.267</t>
+          <t>1119474267003.7</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1269305.703</t>
+          <t>1269305703247.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1432386.005</t>
+          <t>1432386004842.24</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1663242.696</t>
+          <t>1663242696140.46</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1791043.764</t>
+          <t>1791043763714.7</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1788303.482</t>
+          <t>1788303481818.42</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1731252.281</t>
+          <t>1731252280779.37</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1711287.559</t>
+          <t>1711287558900.59</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1740565.303</t>
+          <t>1740565303081.42</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>31527.806</t>
+          <t>31527806202.1259</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>29757.642</t>
+          <t>29757642116.8932</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>23500.175</t>
+          <t>23500175132.4701</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>24777.989</t>
+          <t>24777989358.1375</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>31308.027</t>
+          <t>31308027096.3323</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>43566.493</t>
+          <t>43566492721.8094</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>44952.143</t>
+          <t>44952143396.244</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>45326.52</t>
+          <t>45326520191.0051</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>51271.026</t>
+          <t>51271025781.7133</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>53976.13</t>
+          <t>53976129911.9365</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>74069.778</t>
+          <t>74069777953.2834</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>83004.316</t>
+          <t>83004316294.2896</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>74457.688</t>
+          <t>74457687859.824</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>72407.1</t>
+          <t>72407100439.6407</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>56789.213</t>
+          <t>56789213150.414</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>309888.102</t>
+          <t>309888101922.088</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>334462.108</t>
+          <t>334462107914.639</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>280797.887</t>
+          <t>280797887102.615</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>283971.23</t>
+          <t>283971229925.091</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>386364.589</t>
+          <t>386364588934.43</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>575488.865</t>
+          <t>575488865051.76</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>605374.73</t>
+          <t>605374729991.517</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>649317.576</t>
+          <t>649317576073.123</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>759877.699</t>
+          <t>759877698966.931</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>758185.053</t>
+          <t>758185052848.727</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>912158.402</t>
+          <t>912158401541.9</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1033626.656</t>
+          <t>1033626656050.92</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>817984.81</t>
+          <t>817984809656.743</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>789845.915</t>
+          <t>789845914718.135</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>537182.115</t>
+          <t>537182115051.488</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1108371.608</t>
+          <t>1108371607696.15</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>999464.217</t>
+          <t>999464217237.874</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>881715.723</t>
+          <t>881715723460.532</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>826053.14</t>
+          <t>826053139714.619</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1097714.042</t>
+          <t>1097714042035.98</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1687771.931</t>
+          <t>1687771930655.25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1727795.497</t>
+          <t>1727795497374.8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1638119.274</t>
+          <t>1638119274107.01</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1821168.288</t>
+          <t>1821168287617.41</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1948220.214</t>
+          <t>1948220214153.53</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2290959.725</t>
+          <t>2290959724845.42</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2334714.289</t>
+          <t>2334714289173.12</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1872767.325</t>
+          <t>1872767324561.34</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1960225.883</t>
+          <t>1960225882852.53</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1307505.711</t>
+          <t>1307505710650.4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>258541.85</t>
+          <t>258541849646.809</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>283561.555</t>
+          <t>283561554971.109</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>273353.364</t>
+          <t>273353363870.951</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>216843.941</t>
+          <t>216843941379.977</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>274968.657</t>
+          <t>274968657042.805</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>451325.005</t>
+          <t>451325005001.102</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>460495.891</t>
+          <t>460495891366.138</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>454672.619</t>
+          <t>454672619079.396</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>521374.394</t>
+          <t>521374393689.2</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>555323.435</t>
+          <t>555323435469.162</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>698152.413</t>
+          <t>698152412682.047</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>776803.389</t>
+          <t>776803388954.198</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>643377.495</t>
+          <t>643377495310.038</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>628443.755</t>
+          <t>628443754940.224</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>440963.412</t>
+          <t>440963412046.039</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7335.937</t>
+          <t>7335937132.39483</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9282.019</t>
+          <t>9282018735.21999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9209.274</t>
+          <t>9209274214.6678</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9373.157</t>
+          <t>9373157238.76627</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11253.298</t>
+          <t>11253297728.7073</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11371.328</t>
+          <t>11371328421.8435</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>14474.413</t>
+          <t>14474413452.0806</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13200.099</t>
+          <t>13200099095.7714</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17224.65</t>
+          <t>17224649687.1531</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>20235.767</t>
+          <t>20235766522.5174</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>27758.127</t>
+          <t>27758126760.7486</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>32211.714</t>
+          <t>32211713779.7833</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>42140.023</t>
+          <t>42140023070.2025</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>33275.314</t>
+          <t>33275313502.5227</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>20242.012</t>
+          <t>20242012248.4639</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5894.683</t>
+          <t>5894682799.9152</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5055.833</t>
+          <t>5055832922.49214</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4106.197</t>
+          <t>4106197436.49187</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4834.522</t>
+          <t>4834522206.19189</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6734.044</t>
+          <t>6734043907.74769</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9290.777</t>
+          <t>9290776577.30368</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9083.704</t>
+          <t>9083704023.45076</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8414.842</t>
+          <t>8414842325.60256</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>10003.871</t>
+          <t>10003871253.5916</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>10154.202</t>
+          <t>10154202306.1011</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>12576.464</t>
+          <t>12576463666.7903</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>12947.766</t>
+          <t>12947766203.0674</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>11324.1</t>
+          <t>11324100257.6571</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>11149.274</t>
+          <t>11149273624.8238</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>9623.672</t>
+          <t>9623672378.60393</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2912.664</t>
+          <t>2912663779.54243</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3347.78</t>
+          <t>3347780439.13027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2425.122</t>
+          <t>2425122228.49964</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3327.584</t>
+          <t>3327583668.53544</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4304.96</t>
+          <t>4304960172.89674</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4867.569</t>
+          <t>4867569258.17731</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5996.672</t>
+          <t>5996672059.88648</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6227.793</t>
+          <t>6227792697.33722</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>7448.713</t>
+          <t>7448712689.02651</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9504.08</t>
+          <t>9504079759.15062</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>42269.006</t>
+          <t>42269006255.7435</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>15574.989</t>
+          <t>15574989474.9062</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>12174.888</t>
+          <t>12174887772.3295</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>12164.309</t>
+          <t>12164308757.5218</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>7384.627</t>
+          <t>7384626863.59981</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>65585.517</t>
+          <t>65585516811.8636</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>65536.416</t>
+          <t>65536415676.7185</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>65338.598</t>
+          <t>65338597926.7887</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>82040.889</t>
+          <t>82040888559.2191</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>109517.721</t>
+          <t>109517720671.135</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>158313.823</t>
+          <t>158313822897.315</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>200742.262</t>
+          <t>200742261850.628</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>206114.089</t>
+          <t>206114088845.834</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>199300.702</t>
+          <t>199300701678.372</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>203574.758</t>
+          <t>203574758395.209</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>235221.889</t>
+          <t>235221888507.704</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>232554.271</t>
+          <t>232554270741.394</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>209799.791</t>
+          <t>209799791121.198</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>202431.496</t>
+          <t>202431495527.992</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>140157.552</t>
+          <t>140157551540.299</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1900.667</t>
+          <t>1900667004.63341</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2258.406</t>
+          <t>2258405623.1356</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1519.334</t>
+          <t>1519333738.02462</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1822.588</t>
+          <t>1822588255.00138</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2881.067</t>
+          <t>2881066521.66669</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3706.798</t>
+          <t>3706797631.50566</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4431.673</t>
+          <t>4431673107.57078</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4875.552</t>
+          <t>4875552308.91768</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5265.92</t>
+          <t>5265920222.75714</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4464.886</t>
+          <t>4464886008.54102</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>5606.358</t>
+          <t>5606358448.97883</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>5065.565</t>
+          <t>5065564556.22753</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4200.698</t>
+          <t>4200697542.65662</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>4566.551</t>
+          <t>4566551003.27009</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3136.957</t>
+          <t>3136956623.919</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>197220.328</t>
+          <t>197220327694.121</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>189136.284</t>
+          <t>189136283512.876</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>133288.713</t>
+          <t>133288712692.479</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>176386.022</t>
+          <t>176386022257.266</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>227084.864</t>
+          <t>227084864239.832</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>275592.734</t>
+          <t>275592733836.194</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>293073.25</t>
+          <t>293073249557.192</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>287823.881</t>
+          <t>287823880760.505</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>324075.173</t>
+          <t>324075172583.827</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>316329.238</t>
+          <t>316329237550.998</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>357494.201</t>
+          <t>357494200609.703</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>370713.233</t>
+          <t>370713233342.268</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>331672.919</t>
+          <t>331672919260.357</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>327580.463</t>
+          <t>327580463124.898</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>248615.9</t>
+          <t>248615900357.249</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>44058.02</t>
+          <t>44058020037.0453</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>48588.599</t>
+          <t>48588599179.0015</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>42940.406</t>
+          <t>42940406341.3082</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>54441.371</t>
+          <t>54441371410.7512</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>61896.057</t>
+          <t>61896057470.9251</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>77606.293</t>
+          <t>77606292632.4718</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>78722.25</t>
+          <t>78722249714.1232</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>81536.979</t>
+          <t>81536979261.0878</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>82325.368</t>
+          <t>82325367734.0269</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>87920.337</t>
+          <t>87920336914.7888</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>104535.925</t>
+          <t>104535925017.783</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>109320.872</t>
+          <t>109320872412.235</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>106392.807</t>
+          <t>106392807444.152</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>102988.42</t>
+          <t>102988419724.811</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>69840.509</t>
+          <t>69840509003.7588</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>37477.875</t>
+          <t>37477875241.312</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>37945.354</t>
+          <t>37945353559.503</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>29521.079</t>
+          <t>29521078631.802</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>34125.197</t>
+          <t>34125197291.6243</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>47009.47</t>
+          <t>47009469965.1277</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>75814.899</t>
+          <t>75814899262.2113</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>76897.826</t>
+          <t>76897825591.8585</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>74640.114</t>
+          <t>74640113911.8446</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>81642.953</t>
+          <t>81642953155.7184</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>90704.551</t>
+          <t>90704550725.8742</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>116478.427</t>
+          <t>116478426526.429</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>117815.094</t>
+          <t>117815094234.622</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>103893.598</t>
+          <t>103893598467.873</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>110218.989</t>
+          <t>110218989340.24</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>63964.634</t>
+          <t>63964633920.682</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>34910.182</t>
+          <t>34910181526.7271</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>30847.52</t>
+          <t>30847519587.7243</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24608.074</t>
+          <t>24608073984.2468</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>30960.649</t>
+          <t>30960648669.9026</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>29395.281</t>
+          <t>29395280602.0758</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>42418.733</t>
+          <t>42418733412.6831</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>56106.339</t>
+          <t>56106339199.3445</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>55326.616</t>
+          <t>55326616429.4378</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>63578.19</t>
+          <t>63578189937.2791</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>57422.432</t>
+          <t>57422431669.858</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>73044.791</t>
+          <t>73044791466.3037</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>86170.36</t>
+          <t>86170359529.2953</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>62445.449</t>
+          <t>62445448667.9757</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>76679.851</t>
+          <t>76679851064.1635</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>45955.56</t>
+          <t>45955560119.0468</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>315231.168</t>
+          <t>315231168235.551</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>322542.256</t>
+          <t>322542256187.752</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>234361.308</t>
+          <t>234361308096.288</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>217889.533</t>
+          <t>217889532868.618</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>179869.425</t>
+          <t>179869424783.684</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>256469.863</t>
+          <t>256469863046.173</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>282326.418</t>
+          <t>282326418239.674</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>299284.051</t>
+          <t>299284050921.047</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>337580.713</t>
+          <t>337580712835.462</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>367825.579</t>
+          <t>367825578759.978</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>438024.615</t>
+          <t>438024615465.701</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>461828.29</t>
+          <t>461828289909.146</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>474500.204</t>
+          <t>474500204126.397</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>515809.343</t>
+          <t>515809343158.159</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>371914.589</t>
+          <t>371914589093.667</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4569.502</t>
+          <t>4569501673.71505</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4839.444</t>
+          <t>4839443694.53384</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4376.49</t>
+          <t>4376489966.65583</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5347.397</t>
+          <t>5347396882.65945</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5807.958</t>
+          <t>5807957991.8723</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8270.869</t>
+          <t>8270868682.78749</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9812.362</t>
+          <t>9812362012.27895</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>10211.185</t>
+          <t>10211184699.3593</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>12004.829</t>
+          <t>12004829469.3695</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>18720.93</t>
+          <t>18720930393.9961</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>22343.614</t>
+          <t>22343613710.5604</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>23314.038</t>
+          <t>23314038338.0523</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>25374.006</t>
+          <t>25374006319.7437</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>22291.304</t>
+          <t>22291303656.3195</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>22202.458</t>
+          <t>22202458313.0682</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>14222.484</t>
+          <t>14222483531.1788</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>14413.478</t>
+          <t>14413477558.0046</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10819.19</t>
+          <t>10819189813.9667</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>11382.314</t>
+          <t>11382314382.7801</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>15076.825</t>
+          <t>15076824693.1533</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>19862.855</t>
+          <t>19862855280.7508</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20769.605</t>
+          <t>20769605348.6895</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>22006.125</t>
+          <t>22006124789.1415</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>25903.066</t>
+          <t>25903065552.2066</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>27145.662</t>
+          <t>27145662424.6847</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>30909.569</t>
+          <t>30909568635.6811</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>32191.28</t>
+          <t>32191279625.6025</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>27081.602</t>
+          <t>27081602455.6505</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>40280.295</t>
+          <t>40280295451.5918</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>26841.264</t>
+          <t>26841264207.1878</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>87315.022</t>
+          <t>87315021513.0411</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>89649.929</t>
+          <t>89649928853.1368</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>70165.726</t>
+          <t>70165726233.811</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>79426.214</t>
+          <t>79426213872.2467</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>104169.198</t>
+          <t>104169198309.547</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>151967.459</t>
+          <t>151967459258.934</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>161767.576</t>
+          <t>161767575924.628</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>157505.086</t>
+          <t>157505086147.963</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>185656.69</t>
+          <t>185656689802.447</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>185547.432</t>
+          <t>185547431541.243</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>204678.013</t>
+          <t>204678012822.479</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>200299.958</t>
+          <t>200299957559.464</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>184095.853</t>
+          <t>184095853011.321</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>159773.406</t>
+          <t>159773406206.617</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>104395.907</t>
+          <t>104395906897.119</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>50422.464</t>
+          <t>50422463902.8928</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>59579.122</t>
+          <t>59579121782.8344</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>69752.836</t>
+          <t>69752835513.0491</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>72383.688</t>
+          <t>72383688494.1996</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>92491.087</t>
+          <t>92491087032.1569</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>165848.052</t>
+          <t>165848052190.387</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>154211.45</t>
+          <t>154211449847.693</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>209574.299</t>
+          <t>209574298720.741</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>239960.312</t>
+          <t>239960311702.788</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>249118.441</t>
+          <t>249118441050.2</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>293812.386</t>
+          <t>293812385718.437</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>307152.846</t>
+          <t>307152845681.995</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>266505.439</t>
+          <t>266505438871.387</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>239726.133</t>
+          <t>239726133158.622</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>208923.054</t>
+          <t>208923054116.9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>179895.762</t>
+          <t>179895762030.367</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>178995.371</t>
+          <t>178995371396.701</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>158629.275</t>
+          <t>158629274823.416</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>167829.076</t>
+          <t>167829076288.641</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>228092.673</t>
+          <t>228092673311.701</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>343441.327</t>
+          <t>343441327008.951</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>339514.359</t>
+          <t>339514359245.823</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>352705.784</t>
+          <t>352705783705.003</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>352833.44</t>
+          <t>352833440434.122</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>349424.962</t>
+          <t>349424962447.308</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>374803.711</t>
+          <t>374803710801.789</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>381077.485</t>
+          <t>381077485004.651</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>301136.602</t>
+          <t>301136602221.356</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>299461.473</t>
+          <t>299461473138.367</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>200801.274</t>
+          <t>200801273529.945</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2047624.699</t>
+          <t>2047624698563.78</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2011532.715</t>
+          <t>2011532715462.03</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1886140.685</t>
+          <t>1886140684751.19</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2015978.525</t>
+          <t>2015978524711.47</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2660913.183</t>
+          <t>2660913182943.46</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4175535.065</t>
+          <t>4175535065396.34</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4364292.599</t>
+          <t>4364292599001.02</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4211618.752</t>
+          <t>4211618751982.8</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4486514.094</t>
+          <t>4486514094456.13</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>4528365.845</t>
+          <t>4528365845429.03</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>5347565.708</t>
+          <t>5347565707916.82</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>5280366.304</t>
+          <t>5280366304051.56</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>4400696.313</t>
+          <t>4400696312501.29</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>4225634.994</t>
+          <t>4225634993689.71</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2661952.202</t>
+          <t>2661952201735.75</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>16202666.602</t>
+          <t>16202666602218.8</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15675065.315</t>
+          <t>15675065315011.5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17161914.154</t>
+          <t>17161914154174.9</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>17335892.112</t>
+          <t>17335892111543.1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18719183.74</t>
+          <t>18719183740200.5</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>23116766.291</t>
+          <t>23116766291365.6</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>24159306.286</t>
+          <t>24159306286345</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>23115219.674</t>
+          <t>23115219673553.2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>24611874.432</t>
+          <t>24611874431908.4</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>23605764.714</t>
+          <t>23605764713731.3</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>24100934.604</t>
+          <t>24100934604309.9</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>23452104.966</t>
+          <t>23452104966303.5</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>19330209.148</t>
+          <t>19330209147665.9</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>18927638.216</t>
+          <t>18927638216193.1</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>17319551.772</t>
+          <t>17319551772311.1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>28765802.836</t>
+          <t>28765802835611.2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>27903658.523</t>
+          <t>27903658522935.4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>27922205.907</t>
+          <t>27922205907240.4</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>28060921.54</t>
+          <t>28060921539813.1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>31197338.077</t>
+          <t>31197338077358.3</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>40365447.156</t>
+          <t>40365447155844.4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>42723223.833</t>
+          <t>42723223833419.1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>41922372.436</t>
+          <t>41922372436240.7</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>45176753.77</t>
+          <t>45176753770441.3</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>45428977.28</t>
+          <t>45428977279790.2</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>49028446.749</t>
+          <t>49028446749035.2</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>48853480.003</t>
+          <t>48853480002789.8</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>41567646.106</t>
+          <t>41567646106418.7</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>40972571.508</t>
+          <t>40972571508024</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>33977588.714</t>
+          <t>33977588714043.6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
